--- a/case_studies/2040/technologies.xlsx
+++ b/case_studies/2040/technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\2040\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F88F41D6-540C-4386-954A-66FFB6AE384D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1766A7D0-A364-4B02-AB84-3475C5E3540F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="6168" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="38">
   <si>
     <t>cluster</t>
   </si>
@@ -120,6 +120,21 @@
   </si>
   <si>
     <t>NL4</t>
+  </si>
+  <si>
+    <t>electricity_grid_connection_BE</t>
+  </si>
+  <si>
+    <t>electricity_grid_connection_DE</t>
+  </si>
+  <si>
+    <t>electricity_grid_connection_NL</t>
+  </si>
+  <si>
+    <t>H2_network_connection_in</t>
+  </si>
+  <si>
+    <t>H2_network_connection_out</t>
   </si>
 </sst>
 </file>
@@ -517,8 +532,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AE8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="3" width="10" customWidth="1"/>
@@ -546,7 +561,7 @@
     <col min="25" max="26" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -625,8 +640,23 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>26</v>
       </c>
@@ -705,8 +735,23 @@
       <c r="Z2" s="3">
         <v>34.49</v>
       </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>27</v>
       </c>
@@ -785,8 +830,23 @@
       <c r="Z3" s="5">
         <v>43.78</v>
       </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
@@ -865,8 +925,23 @@
       <c r="Z4" s="3">
         <v>38.74</v>
       </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>29</v>
       </c>
@@ -945,8 +1020,23 @@
       <c r="Z5" s="5">
         <v>0</v>
       </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>30</v>
       </c>
@@ -1025,8 +1115,23 @@
       <c r="Z6" s="3">
         <v>0</v>
       </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>31</v>
       </c>
@@ -1105,8 +1210,23 @@
       <c r="Z7" s="5">
         <v>0</v>
       </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
@@ -1183,6 +1303,21 @@
         <v>0</v>
       </c>
       <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
         <v>0</v>
       </c>
     </row>
@@ -1193,8 +1328,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04496ABF-FD19-41A9-8521-307709114B17}">
-  <dimension ref="A1:Z8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AE8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="3" width="10" customWidth="1"/>
@@ -1222,7 +1357,7 @@
     <col min="25" max="26" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1301,8 +1436,23 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>26</v>
       </c>
@@ -1381,8 +1531,23 @@
       <c r="Z2" s="3">
         <v>1</v>
       </c>
+      <c r="AA2">
+        <v>1</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>1</v>
+      </c>
+      <c r="AE2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>27</v>
       </c>
@@ -1461,8 +1626,23 @@
       <c r="Z3" s="5">
         <v>1</v>
       </c>
+      <c r="AA3">
+        <v>1</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>1</v>
+      </c>
+      <c r="AE3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
@@ -1541,8 +1721,23 @@
       <c r="Z4" s="3">
         <v>1</v>
       </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>1</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>1</v>
+      </c>
+      <c r="AE4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>29</v>
       </c>
@@ -1621,8 +1816,23 @@
       <c r="Z5" s="5">
         <v>1</v>
       </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>1</v>
+      </c>
+      <c r="AD5">
+        <v>1</v>
+      </c>
+      <c r="AE5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>30</v>
       </c>
@@ -1701,8 +1911,23 @@
       <c r="Z6" s="3">
         <v>1</v>
       </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AD6">
+        <v>1</v>
+      </c>
+      <c r="AE6">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>31</v>
       </c>
@@ -1781,8 +2006,23 @@
       <c r="Z7" s="5">
         <v>1</v>
       </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>1</v>
+      </c>
+      <c r="AD7">
+        <v>1</v>
+      </c>
+      <c r="AE7">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
@@ -1859,6 +2099,21 @@
         <v>1</v>
       </c>
       <c r="Z8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AD8">
+        <v>1</v>
+      </c>
+      <c r="AE8">
         <v>1</v>
       </c>
     </row>

--- a/case_studies/2040/technologies.xlsx
+++ b/case_studies/2040/technologies.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\2040\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1766A7D0-A364-4B02-AB84-3475C5E3540F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7AD6CC5-D770-4FCA-917F-BB7D6AC5D2DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="1" r:id="rId1"/>
-    <sheet name="new" sheetId="3" r:id="rId2"/>
+    <sheet name="new" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -101,6 +101,21 @@
     <t>CO2toEmissions</t>
   </si>
   <si>
+    <t>electricity_grid_connection_BE</t>
+  </si>
+  <si>
+    <t>electricity_grid_connection_DE</t>
+  </si>
+  <si>
+    <t>electricity_grid_connection_NL</t>
+  </si>
+  <si>
+    <t>H2_network_connection_in</t>
+  </si>
+  <si>
+    <t>H2_network_connection_out</t>
+  </si>
+  <si>
     <t>BEL1</t>
   </si>
   <si>
@@ -120,21 +135,6 @@
   </si>
   <si>
     <t>NL4</t>
-  </si>
-  <si>
-    <t>electricity_grid_connection_BE</t>
-  </si>
-  <si>
-    <t>electricity_grid_connection_DE</t>
-  </si>
-  <si>
-    <t>electricity_grid_connection_NL</t>
-  </si>
-  <si>
-    <t>H2_network_connection_in</t>
-  </si>
-  <si>
-    <t>H2_network_connection_out</t>
   </si>
 </sst>
 </file>
@@ -559,6 +559,9 @@
     <col min="23" max="23" width="11" customWidth="1"/>
     <col min="24" max="24" width="15" customWidth="1"/>
     <col min="25" max="26" width="16" customWidth="1"/>
+    <col min="27" max="29" width="32" customWidth="1"/>
+    <col min="30" max="30" width="26" customWidth="1"/>
+    <col min="31" max="31" width="27" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -640,25 +643,25 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>37</v>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
@@ -688,10 +691,10 @@
         <v>78.38</v>
       </c>
       <c r="K2" s="3">
-        <v>249.27</v>
+        <v>244.67</v>
       </c>
       <c r="L2" s="3">
-        <v>118.8</v>
+        <v>116.63</v>
       </c>
       <c r="M2" s="3">
         <v>723.41</v>
@@ -715,7 +718,7 @@
         <v>0</v>
       </c>
       <c r="T2" s="3">
-        <v>171.8</v>
+        <v>169.63</v>
       </c>
       <c r="U2" s="3">
         <v>0</v>
@@ -733,27 +736,27 @@
         <v>0</v>
       </c>
       <c r="Z2" s="3">
-        <v>34.49</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
+        <v>28.54</v>
+      </c>
+      <c r="AA2" s="3">
+        <v>681.27</v>
+      </c>
+      <c r="AB2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="3">
+        <v>57.5</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B3" s="5">
         <v>5.21</v>
@@ -830,25 +833,25 @@
       <c r="Z3" s="5">
         <v>43.78</v>
       </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
+      <c r="AA3" s="5">
+        <v>66.739999999999995</v>
+      </c>
+      <c r="AB3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
@@ -869,34 +872,34 @@
         <v>7.07</v>
       </c>
       <c r="H4" s="3">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="3">
         <v>0</v>
       </c>
       <c r="J4" s="3">
-        <v>35.229999999999997</v>
+        <v>108.66</v>
       </c>
       <c r="K4" s="3">
         <v>30.09</v>
       </c>
       <c r="L4" s="3">
-        <v>26.93</v>
+        <v>30.93</v>
       </c>
       <c r="M4" s="3">
-        <v>480.85</v>
+        <v>1260</v>
       </c>
       <c r="N4" s="3">
-        <v>480.85</v>
+        <v>1260</v>
       </c>
       <c r="O4" s="3">
         <v>0</v>
       </c>
       <c r="P4" s="3">
-        <v>27.13</v>
+        <v>35.61</v>
       </c>
       <c r="Q4" s="3">
-        <v>2.95</v>
+        <v>3.43</v>
       </c>
       <c r="R4" s="3">
         <v>0</v>
@@ -905,7 +908,7 @@
         <v>0</v>
       </c>
       <c r="T4" s="3">
-        <v>26.93</v>
+        <v>70.56</v>
       </c>
       <c r="U4" s="3">
         <v>0</v>
@@ -917,7 +920,7 @@
         <v>0</v>
       </c>
       <c r="X4" s="3">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="Y4" s="3">
         <v>0</v>
@@ -925,28 +928,28 @@
       <c r="Z4" s="3">
         <v>38.74</v>
       </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
+      <c r="AA4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="3">
+        <v>393.66</v>
+      </c>
+      <c r="AC4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B5" s="5">
-        <v>24.73</v>
+        <v>0</v>
       </c>
       <c r="C5" s="5">
         <v>0</v>
@@ -964,43 +967,43 @@
         <v>38.39</v>
       </c>
       <c r="H5" s="5">
-        <v>16.309999999999999</v>
+        <v>10.86</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>36.770000000000003</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>6.06</v>
       </c>
       <c r="M5" s="5">
-        <v>0</v>
+        <v>643.22</v>
       </c>
       <c r="N5" s="5">
-        <v>0</v>
+        <v>643.22</v>
       </c>
       <c r="O5" s="5">
         <v>0</v>
       </c>
       <c r="P5" s="5">
-        <v>0</v>
+        <v>7.67</v>
       </c>
       <c r="Q5" s="5">
         <v>0</v>
       </c>
       <c r="R5" s="5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="S5" s="5">
         <v>0</v>
       </c>
       <c r="T5" s="5">
-        <v>0</v>
+        <v>6.06</v>
       </c>
       <c r="U5" s="5">
         <v>0</v>
@@ -1020,28 +1023,28 @@
       <c r="Z5" s="5">
         <v>0</v>
       </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0</v>
-      </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
+      <c r="AA5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="5">
+        <v>177.05</v>
+      </c>
+      <c r="AD5" s="5">
+        <v>38.409999999999997</v>
+      </c>
+      <c r="AE5" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B6" s="3">
-        <v>0.71</v>
+        <v>0.42</v>
       </c>
       <c r="C6" s="3">
         <v>0</v>
@@ -1065,13 +1068,13 @@
         <v>0</v>
       </c>
       <c r="J6" s="3">
-        <v>40.14</v>
+        <v>46.82</v>
       </c>
       <c r="K6" s="3">
         <v>0</v>
       </c>
       <c r="L6" s="3">
-        <v>31.35</v>
+        <v>0</v>
       </c>
       <c r="M6" s="3">
         <v>396.62</v>
@@ -1083,19 +1086,19 @@
         <v>0</v>
       </c>
       <c r="P6" s="3">
-        <v>66.7</v>
+        <v>0.04</v>
       </c>
       <c r="Q6" s="3">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="R6" s="3">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="S6" s="3">
         <v>0</v>
       </c>
       <c r="T6" s="3">
-        <v>58.08</v>
+        <v>31.66</v>
       </c>
       <c r="U6" s="3">
         <v>0</v>
@@ -1115,25 +1118,25 @@
       <c r="Z6" s="3">
         <v>0</v>
       </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
+      <c r="AA6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="3">
+        <v>160.51</v>
+      </c>
+      <c r="AD6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B7" s="5">
         <v>0</v>
@@ -1160,13 +1163,13 @@
         <v>0</v>
       </c>
       <c r="J7" s="5">
-        <v>0</v>
+        <v>9.6199999999999992</v>
       </c>
       <c r="K7" s="5">
         <v>0</v>
       </c>
       <c r="L7" s="5">
-        <v>45.66</v>
+        <v>37.32</v>
       </c>
       <c r="M7" s="5">
         <v>0</v>
@@ -1178,19 +1181,19 @@
         <v>0</v>
       </c>
       <c r="P7" s="5">
-        <v>97.03</v>
+        <v>86.21</v>
       </c>
       <c r="Q7" s="5">
         <v>0</v>
       </c>
       <c r="R7" s="5">
-        <v>0</v>
+        <v>8.94</v>
       </c>
       <c r="S7" s="5">
-        <v>0</v>
+        <v>7.36</v>
       </c>
       <c r="T7" s="5">
-        <v>45.66</v>
+        <v>37.32</v>
       </c>
       <c r="U7" s="5">
         <v>0</v>
@@ -1199,7 +1202,7 @@
         <v>0</v>
       </c>
       <c r="W7" s="5">
-        <v>0</v>
+        <v>8.94</v>
       </c>
       <c r="X7" s="5">
         <v>0</v>
@@ -1210,25 +1213,25 @@
       <c r="Z7" s="5">
         <v>0</v>
       </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
+      <c r="AA7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="5">
+        <v>161.87</v>
+      </c>
+      <c r="AD7" s="5">
+        <v>1.63</v>
+      </c>
+      <c r="AE7" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
@@ -1255,13 +1258,13 @@
         <v>0</v>
       </c>
       <c r="J8" s="3">
-        <v>146.22999999999999</v>
+        <v>147.41</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
       </c>
       <c r="L8" s="3">
-        <v>90.03</v>
+        <v>0</v>
       </c>
       <c r="M8" s="3">
         <v>136.33000000000001</v>
@@ -1273,28 +1276,28 @@
         <v>0</v>
       </c>
       <c r="P8" s="3">
-        <v>279.76</v>
+        <v>74.23</v>
       </c>
       <c r="Q8" s="3">
-        <v>311.87</v>
+        <v>103.24</v>
       </c>
       <c r="R8" s="3">
-        <v>114.45</v>
+        <v>96.07</v>
       </c>
       <c r="S8" s="3">
-        <v>21.68</v>
+        <v>19.54</v>
       </c>
       <c r="T8" s="3">
-        <v>118.81</v>
+        <v>36.58</v>
       </c>
       <c r="U8" s="3">
         <v>0</v>
       </c>
       <c r="V8" s="3">
-        <v>0.76</v>
+        <v>0.9</v>
       </c>
       <c r="W8" s="3">
-        <v>113.95</v>
+        <v>95.63</v>
       </c>
       <c r="X8" s="3">
         <v>0</v>
@@ -1305,19 +1308,19 @@
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0</v>
-      </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>364.79</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>17.46</v>
+      </c>
+      <c r="AE8" s="3">
         <v>0</v>
       </c>
     </row>
@@ -1327,7 +1330,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04496ABF-FD19-41A9-8521-307709114B17}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B9A2314-B8AF-42CC-BE94-663706F5011D}">
   <dimension ref="A1:AE8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1355,6 +1358,9 @@
     <col min="23" max="23" width="11" customWidth="1"/>
     <col min="24" max="24" width="15" customWidth="1"/>
     <col min="25" max="26" width="16" customWidth="1"/>
+    <col min="27" max="29" width="32" customWidth="1"/>
+    <col min="30" max="30" width="26" customWidth="1"/>
+    <col min="31" max="31" width="27" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1436,25 +1442,25 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>37</v>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -1531,25 +1537,25 @@
       <c r="Z2" s="3">
         <v>1</v>
       </c>
-      <c r="AA2">
-        <v>1</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>1</v>
-      </c>
-      <c r="AE2">
+      <c r="AA2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B3" s="5">
         <v>1</v>
@@ -1626,25 +1632,25 @@
       <c r="Z3" s="5">
         <v>1</v>
       </c>
-      <c r="AA3">
-        <v>1</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>1</v>
-      </c>
-      <c r="AE3">
+      <c r="AA3" s="5">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="5">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3">
         <v>1</v>
@@ -1721,25 +1727,25 @@
       <c r="Z4" s="3">
         <v>1</v>
       </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>1</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>1</v>
-      </c>
-      <c r="AE4">
+      <c r="AA4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B5" s="5">
         <v>1</v>
@@ -1816,25 +1822,25 @@
       <c r="Z5" s="5">
         <v>1</v>
       </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0</v>
-      </c>
-      <c r="AC5">
-        <v>1</v>
-      </c>
-      <c r="AD5">
-        <v>1</v>
-      </c>
-      <c r="AE5">
+      <c r="AA5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="5">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="5">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1911,25 +1917,25 @@
       <c r="Z6" s="3">
         <v>1</v>
       </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <v>1</v>
-      </c>
-      <c r="AD6">
-        <v>1</v>
-      </c>
-      <c r="AE6">
+      <c r="AA6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B7" s="5">
         <v>1</v>
@@ -2006,25 +2012,25 @@
       <c r="Z7" s="5">
         <v>1</v>
       </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>1</v>
-      </c>
-      <c r="AD7">
-        <v>1</v>
-      </c>
-      <c r="AE7">
+      <c r="AA7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="5">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="5">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -2101,19 +2107,19 @@
       <c r="Z8" s="3">
         <v>1</v>
       </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0</v>
-      </c>
-      <c r="AC8">
-        <v>1</v>
-      </c>
-      <c r="AD8">
-        <v>1</v>
-      </c>
-      <c r="AE8">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="3">
         <v>1</v>
       </c>
     </row>

--- a/case_studies/2040/technologies.xlsx
+++ b/case_studies/2040/technologies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\2040\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7AD6CC5-D770-4FCA-917F-BB7D6AC5D2DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_FDB96DFE4F5C903720334DD4235BDA1626C6A632" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="1" r:id="rId1"/>
@@ -533,7 +533,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="3" width="10" customWidth="1"/>
@@ -564,7 +564,7 @@
     <col min="31" max="31" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -659,7 +659,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>31</v>
       </c>
@@ -739,7 +739,7 @@
         <v>28.54</v>
       </c>
       <c r="AA2" s="3">
-        <v>681.27</v>
+        <v>0</v>
       </c>
       <c r="AB2" s="3">
         <v>0</v>
@@ -751,10 +751,10 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3">
-        <v>57.5</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>32</v>
       </c>
@@ -834,7 +834,7 @@
         <v>43.78</v>
       </c>
       <c r="AA3" s="5">
-        <v>66.739999999999995</v>
+        <v>0</v>
       </c>
       <c r="AB3" s="5">
         <v>0</v>
@@ -849,7 +849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>33</v>
       </c>
@@ -932,7 +932,7 @@
         <v>0</v>
       </c>
       <c r="AB4" s="3">
-        <v>393.66</v>
+        <v>0</v>
       </c>
       <c r="AC4" s="3">
         <v>0</v>
@@ -944,7 +944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>34</v>
       </c>
@@ -1030,16 +1030,16 @@
         <v>0</v>
       </c>
       <c r="AC5" s="5">
-        <v>177.05</v>
+        <v>0</v>
       </c>
       <c r="AD5" s="5">
-        <v>38.409999999999997</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>35</v>
       </c>
@@ -1125,7 +1125,7 @@
         <v>0</v>
       </c>
       <c r="AC6" s="3">
-        <v>160.51</v>
+        <v>0</v>
       </c>
       <c r="AD6" s="3">
         <v>0</v>
@@ -1134,7 +1134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>36</v>
       </c>
@@ -1220,16 +1220,16 @@
         <v>0</v>
       </c>
       <c r="AC7" s="5">
-        <v>161.87</v>
+        <v>0</v>
       </c>
       <c r="AD7" s="5">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>37</v>
       </c>
@@ -1315,10 +1315,10 @@
         <v>0</v>
       </c>
       <c r="AC8" s="3">
-        <v>364.79</v>
+        <v>0</v>
       </c>
       <c r="AD8" s="3">
-        <v>17.46</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="3">
         <v>0</v>
@@ -1330,9 +1330,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B9A2314-B8AF-42CC-BE94-663706F5011D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="3" width="10" customWidth="1"/>
@@ -1363,7 +1363,7 @@
     <col min="31" max="31" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1458,7 +1458,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>31</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>32</v>
       </c>
@@ -1648,7 +1648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>33</v>
       </c>
@@ -1743,7 +1743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>34</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>35</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>36</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>37</v>
       </c>
